--- a/eeg_emotion/outputs/submission.xlsx
+++ b/eeg_emotion/outputs/submission.xlsx
@@ -547,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -664,7 +664,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -716,7 +716,7 @@
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -729,7 +729,7 @@
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -781,7 +781,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -807,7 +807,7 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -820,7 +820,7 @@
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -846,7 +846,7 @@
         <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -872,7 +872,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1171,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1223,7 +1223,7 @@
         <v>5</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1327,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1366,7 +1366,7 @@
         <v>8</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1392,7 +1392,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -1405,7 +1405,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
